--- a/data/trans_dic/P64D$bicicleta_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$bicicleta_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,45</t>
+          <t>0,24; 4,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,8</t>
+          <t>0,16; 3,35</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,0</t>
+          <t>0,46; 2,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 29,04</t>
+          <t>0,37; 29,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 13,96</t>
+          <t>0,69; 15,03</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,46</t>
+          <t>0,94; 3,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,37</t>
+          <t>0,55; 2,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,62</t>
+          <t>0,97; 2,49</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,93</t>
+          <t>0,74; 1,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 22,5</t>
+          <t>0,55; 20,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,77</t>
+          <t>0,9; 11,25</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>323; 5885</t>
+          <t>316; 6313</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1264</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>331; 5950</t>
+          <t>333; 7124</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6698; 27627</t>
+          <t>6396; 27812</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3385; 274404</t>
+          <t>3534; 280571</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15981; 324989</t>
+          <t>16015; 349697</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4168; 15456</t>
+          <t>4195; 16126</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2097; 10298</t>
+          <t>2404; 10286</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8331; 23151</t>
+          <t>8562; 22011</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14167; 37768</t>
+          <t>14492; 38075</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8597; 328623</t>
+          <t>7981; 299919</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30609; 368639</t>
+          <t>30644; 385109</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$bicicleta_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$bicicleta_2023-Estudios-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,78</t>
+          <t>1,29; 14,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,35</t>
+          <t>0,86; 10,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,01</t>
+          <t>0,89; 2,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 29,69</t>
+          <t>0,5; 1,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 15,03</t>
+          <t>0,87; 2,01</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,61</t>
+          <t>1,09; 4,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,36</t>
+          <t>0,82; 2,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,49</t>
+          <t>1,1; 2,74</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,94</t>
+          <t>1,35; 3,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 20,53</t>
+          <t>0,69; 1,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 11,25</t>
+          <t>1,16; 2,26</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>8683</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>316; 6313</t>
+          <t>2120; 24235</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>333; 7124</t>
+          <t>2158; 26268</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74195</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88780</t>
+          <t>28633</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6396; 27812</t>
+          <t>11349; 34310</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3534; 280571</t>
+          <t>4761; 15706</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16015; 349697</t>
+          <t>19168; 44478</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>17928</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4195; 16126</t>
+          <t>5327; 19770</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2404; 10286</t>
+          <t>3924; 13833</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8562; 22011</t>
+          <t>10657; 26476</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>24970</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>55245</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14492; 38075</t>
+          <t>25905; 61699</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7981; 299919</t>
+          <t>10366; 24655</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30644; 385109</t>
+          <t>39980; 77730</t>
         </is>
       </c>
     </row>
